--- a/VerveStacks_DEU_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_DEU_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91C4B18D-4DD2-456C-8E26-B690EA12AD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FF0B702-9390-4262-84A4-90CFFF379BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -778,7 +778,7 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S03aH02,S03aH01,S01aH02,S02aH01,S01aH01</t>
+    <t>S03aH02,S03aH01,S02aH02,S01aH02,S02aH01,S01aH01</t>
   </si>
   <si>
     <t>N</t>
@@ -922,10 +922,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH05,S05aH05,S06aH04,S01aH03,S05aH02,S05aH03,S02aH02,S01aH05,S06aH05,S01aH04,S07aH02,S02aH03,S07aH03,S03aH02,S07aH05,S01aH02,S04aH04,S02aH04,S02aH05,S04aH02,S04aH03,S07aH04,S05aH04,S06aH02,S06aH03,S03aH04,S03aH03,S04aH05</t>
+    <t>S02aH03,S07aH03,S02aH02,S05aH04,S06aH02,S06aH03,S01aH02,S04aH04,S03aH04,S04aH03,S07aH04,S03aH03,S04aH02,S02aH04,S02aH05,S01aH03,S05aH02,S05aH03,S03aH02,S07aH05,S01aH04,S07aH02,S04aH05,S03aH05,S05aH05,S06aH04,S01aH05,S06aH05</t>
   </si>
   <si>
-    <t>S03aH01,S06aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH06,S02aH01,S05aH06,S01aH06,S07aH01,S05aH01,S07aH06,S06aH06</t>
+    <t>S01aH01,S04aH01,S04aH06,S03aH01,S01aH06,S07aH01,S03aH06,S05aH01,S07aH06,S02aH01,S05aH06,S06aH06,S02aH06,S06aH01</t>
   </si>
   <si>
     <t>AllS</t>
@@ -991,10 +991,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,FaD,RaD,FaP,SaP,RaP,WaD,WaP</t>
+    <t>SaD,RaP,RaD,WaP,FaD,FaP,SaP,WaD</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,WaP,SaN,WaN,FaN,RaN</t>
+    <t>FaP,SaP,SaN,WaN,RaN,RaP,WaP,FaN</t>
   </si>
 </sst>
 </file>
@@ -24655,7 +24655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5229E6A9-7C27-4082-926C-4882B429DD4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F82E93-A9E7-4485-882D-67D18E386582}">
   <dimension ref="A9:AN217"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25222,7 +25222,7 @@
         <v>159</v>
       </c>
       <c r="AM15">
-        <v>0.43010548667828774</v>
+        <v>0.43010548667828763</v>
       </c>
       <c r="AN15" t="s">
         <v>238</v>
@@ -25660,7 +25660,7 @@
         <v>159</v>
       </c>
       <c r="AM21">
-        <v>0.42941250000000003</v>
+        <v>0.42941249999999997</v>
       </c>
       <c r="AN21" t="s">
         <v>238</v>
@@ -26014,7 +26014,7 @@
         <v>159</v>
       </c>
       <c r="AM27">
-        <v>0.34230000000000005</v>
+        <v>0.34229999999999999</v>
       </c>
       <c r="AN27" t="s">
         <v>238</v>
@@ -26473,7 +26473,7 @@
         <v>159</v>
       </c>
       <c r="AM36">
-        <v>0.35376250000000004</v>
+        <v>0.35376249999999998</v>
       </c>
       <c r="AN36" t="s">
         <v>238</v>
@@ -26623,7 +26623,7 @@
         <v>159</v>
       </c>
       <c r="AM39">
-        <v>0.34997500000000004</v>
+        <v>0.34997499999999998</v>
       </c>
       <c r="AN39" t="s">
         <v>238</v>
@@ -27073,7 +27073,7 @@
         <v>159</v>
       </c>
       <c r="AM48">
-        <v>0.41247499999999993</v>
+        <v>0.41247500000000004</v>
       </c>
       <c r="AN48" t="s">
         <v>238</v>
@@ -27223,7 +27223,7 @@
         <v>159</v>
       </c>
       <c r="AM51">
-        <v>0.39565</v>
+        <v>0.39564999999999995</v>
       </c>
       <c r="AN51" t="s">
         <v>238</v>
@@ -27373,7 +27373,7 @@
         <v>159</v>
       </c>
       <c r="AM54">
-        <v>0.40179999999999999</v>
+        <v>0.40180000000000005</v>
       </c>
       <c r="AN54" t="s">
         <v>238</v>
@@ -27523,7 +27523,7 @@
         <v>159</v>
       </c>
       <c r="AM57">
-        <v>0.39618749999999997</v>
+        <v>0.39618750000000003</v>
       </c>
       <c r="AN57" t="s">
         <v>238</v>
@@ -27823,7 +27823,7 @@
         <v>159</v>
       </c>
       <c r="AM63">
-        <v>0.408275</v>
+        <v>0.40827499999999994</v>
       </c>
       <c r="AN63" t="s">
         <v>238</v>
@@ -28423,7 +28423,7 @@
         <v>159</v>
       </c>
       <c r="AM75">
-        <v>0.40817500000000001</v>
+        <v>0.40817499999999995</v>
       </c>
       <c r="AN75" t="s">
         <v>238</v>
@@ -28723,7 +28723,7 @@
         <v>159</v>
       </c>
       <c r="AM81">
-        <v>0.39603749999999999</v>
+        <v>0.39603749999999993</v>
       </c>
       <c r="AN81" t="s">
         <v>238</v>
@@ -29323,7 +29323,7 @@
         <v>159</v>
       </c>
       <c r="AM93">
-        <v>0.40751249999999994</v>
+        <v>0.4075125</v>
       </c>
       <c r="AN93" t="s">
         <v>238</v>
@@ -32583,7 +32583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F2B67E-3BD8-42BF-99A6-496EFAF497B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D305863-F5C1-47F8-B858-8F96A8079EC4}">
   <dimension ref="A9:AN976"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34300,7 +34300,7 @@
         <v>242</v>
       </c>
       <c r="AM29">
-        <v>0.34101200270411602</v>
+        <v>0.34101200270411608</v>
       </c>
       <c r="AN29" t="s">
         <v>238</v>
@@ -35420,7 +35420,7 @@
         <v>242</v>
       </c>
       <c r="AM43">
-        <v>0.32382</v>
+        <v>0.32382000000000005</v>
       </c>
       <c r="AN43" t="s">
         <v>238</v>
@@ -37674,7 +37674,7 @@
         <v>242</v>
       </c>
       <c r="AM78">
-        <v>0.34265999999999996</v>
+        <v>0.34266000000000002</v>
       </c>
       <c r="AN78" t="s">
         <v>238</v>
@@ -38087,7 +38087,7 @@
         <v>242</v>
       </c>
       <c r="AM85">
-        <v>0.4032400000000001</v>
+        <v>0.40323999999999999</v>
       </c>
       <c r="AN85" t="s">
         <v>238</v>
@@ -38868,7 +38868,7 @@
         <v>242</v>
       </c>
       <c r="AM99">
-        <v>0.41937999999999998</v>
+        <v>0.41938000000000003</v>
       </c>
       <c r="AN99" t="s">
         <v>238</v>
@@ -39568,7 +39568,7 @@
         <v>242</v>
       </c>
       <c r="AM113">
-        <v>0.39845999999999998</v>
+        <v>0.39846000000000004</v>
       </c>
       <c r="AN113" t="s">
         <v>238</v>
@@ -39918,7 +39918,7 @@
         <v>242</v>
       </c>
       <c r="AM120">
-        <v>0.37730000000000002</v>
+        <v>0.37729999999999997</v>
       </c>
       <c r="AN120" t="s">
         <v>238</v>
@@ -40268,7 +40268,7 @@
         <v>242</v>
       </c>
       <c r="AM127">
-        <v>0.39101999999999998</v>
+        <v>0.39102000000000003</v>
       </c>
       <c r="AN127" t="s">
         <v>238</v>
@@ -41318,7 +41318,7 @@
         <v>242</v>
       </c>
       <c r="AM148">
-        <v>0.38603999999999999</v>
+        <v>0.38604000000000005</v>
       </c>
       <c r="AN148" t="s">
         <v>238</v>
@@ -42368,7 +42368,7 @@
         <v>242</v>
       </c>
       <c r="AM169">
-        <v>0.40207999999999994</v>
+        <v>0.40208000000000005</v>
       </c>
       <c r="AN169" t="s">
         <v>238</v>
@@ -43068,7 +43068,7 @@
         <v>242</v>
       </c>
       <c r="AM183">
-        <v>0.40822000000000003</v>
+        <v>0.40821999999999992</v>
       </c>
       <c r="AN183" t="s">
         <v>238</v>
@@ -44118,7 +44118,7 @@
         <v>242</v>
       </c>
       <c r="AM204">
-        <v>0.39584000000000003</v>
+        <v>0.39583999999999997</v>
       </c>
       <c r="AN204" t="s">
         <v>238</v>
@@ -66518,7 +66518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40EAE85D-A5A8-47D1-B5CD-1671BA64752B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3221F889-51DF-40CB-BFDD-248268D9FEA4}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -66747,7 +66747,7 @@
         <v>282</v>
       </c>
       <c r="AM11">
-        <v>0.38802670653427357</v>
+        <v>0.38802670653427351</v>
       </c>
       <c r="AN11" t="s">
         <v>238</v>
@@ -66906,7 +66906,7 @@
         <v>282</v>
       </c>
       <c r="AM14">
-        <v>0.40299166666666669</v>
+        <v>0.40299166666666664</v>
       </c>
       <c r="AN14" t="s">
         <v>238</v>
@@ -67056,7 +67056,7 @@
         <v>282</v>
       </c>
       <c r="AM17">
-        <v>0.32603333333333334</v>
+        <v>0.32603333333333329</v>
       </c>
       <c r="AN17" t="s">
         <v>238</v>
@@ -67206,7 +67206,7 @@
         <v>282</v>
       </c>
       <c r="AM20">
-        <v>0.33071666666666671</v>
+        <v>0.33071666666666666</v>
       </c>
       <c r="AN20" t="s">
         <v>238</v>
@@ -67244,7 +67244,7 @@
         <v>282</v>
       </c>
       <c r="AM21">
-        <v>0.38834166666666675</v>
+        <v>0.38834166666666664</v>
       </c>
       <c r="AN21" t="s">
         <v>238</v>
@@ -67282,7 +67282,7 @@
         <v>282</v>
       </c>
       <c r="AM22">
-        <v>0.39006666666666662</v>
+        <v>0.39006666666666673</v>
       </c>
       <c r="AN22" t="s">
         <v>238</v>
@@ -67320,7 +67320,7 @@
         <v>282</v>
       </c>
       <c r="AM23">
-        <v>0.38800833333333329</v>
+        <v>0.38800833333333334</v>
       </c>
       <c r="AN23" t="s">
         <v>238</v>
@@ -67396,7 +67396,7 @@
         <v>282</v>
       </c>
       <c r="AM25">
-        <v>0.3893416666666667</v>
+        <v>0.38934166666666664</v>
       </c>
       <c r="AN25" t="s">
         <v>238</v>
@@ -67472,7 +67472,7 @@
         <v>282</v>
       </c>
       <c r="AM27">
-        <v>0.37599999999999995</v>
+        <v>0.37600000000000006</v>
       </c>
       <c r="AN27" t="s">
         <v>238</v>
@@ -67716,7 +67716,7 @@
         <v>282</v>
       </c>
       <c r="AM35">
-        <v>0.38488333333333341</v>
+        <v>0.3848833333333333</v>
       </c>
       <c r="AN35" t="s">
         <v>238</v>
@@ -67730,7 +67730,7 @@
         <v>282</v>
       </c>
       <c r="AM36">
-        <v>0.38367499999999999</v>
+        <v>0.38367500000000004</v>
       </c>
       <c r="AN36" t="s">
         <v>238</v>
@@ -67744,7 +67744,7 @@
         <v>282</v>
       </c>
       <c r="AM37">
-        <v>0.38875833333333337</v>
+        <v>0.38875833333333326</v>
       </c>
       <c r="AN37" t="s">
         <v>238</v>
@@ -67772,7 +67772,7 @@
         <v>282</v>
       </c>
       <c r="AM39">
-        <v>0.37451666666666661</v>
+        <v>0.37451666666666666</v>
       </c>
       <c r="AN39" t="s">
         <v>238</v>
@@ -67784,7 +67784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E1C637-2E64-4EDC-9098-4D2D6F63900A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B0BEA4-9ACF-4856-B8CB-094C97024D70}">
   <dimension ref="A9:AN286"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -68013,7 +68013,7 @@
         <v>285</v>
       </c>
       <c r="AM11">
-        <v>0.376892133328949</v>
+        <v>0.37689213332894894</v>
       </c>
       <c r="AN11" t="s">
         <v>238</v>
@@ -68102,7 +68102,7 @@
         <v>287</v>
       </c>
       <c r="AM12">
-        <v>0.39410081878267728</v>
+        <v>0.39410081878267733</v>
       </c>
       <c r="AN12" t="s">
         <v>238</v>
@@ -68354,7 +68354,7 @@
         <v>285</v>
       </c>
       <c r="AM15">
-        <v>0.32311381832505282</v>
+        <v>0.32311381832505287</v>
       </c>
       <c r="AN15" t="s">
         <v>238</v>
@@ -69091,7 +69091,7 @@
         <v>288</v>
       </c>
       <c r="AM25">
-        <v>0.44846666666666662</v>
+        <v>0.44846666666666674</v>
       </c>
       <c r="AN25" t="s">
         <v>238</v>
@@ -69386,7 +69386,7 @@
         <v>290</v>
       </c>
       <c r="AM30">
-        <v>0.29203333333333337</v>
+        <v>0.29203333333333331</v>
       </c>
       <c r="AN30" t="s">
         <v>238</v>
@@ -69822,7 +69822,7 @@
         <v>290</v>
       </c>
       <c r="AM38">
-        <v>0.28049999999999997</v>
+        <v>0.28050000000000003</v>
       </c>
       <c r="AN38" t="s">
         <v>238</v>
@@ -70022,7 +70022,7 @@
         <v>290</v>
       </c>
       <c r="AM42">
-        <v>0.31263333333333332</v>
+        <v>0.31263333333333337</v>
       </c>
       <c r="AN42" t="s">
         <v>238</v>
@@ -70072,7 +70072,7 @@
         <v>285</v>
       </c>
       <c r="AM43">
-        <v>0.29209999999999997</v>
+        <v>0.29210000000000003</v>
       </c>
       <c r="AN43" t="s">
         <v>238</v>
@@ -70272,7 +70272,7 @@
         <v>285</v>
       </c>
       <c r="AM47">
-        <v>0.28260000000000002</v>
+        <v>0.28259999999999996</v>
       </c>
       <c r="AN47" t="s">
         <v>238</v>
@@ -70822,7 +70822,7 @@
         <v>290</v>
       </c>
       <c r="AM58">
-        <v>0.34769999999999995</v>
+        <v>0.34770000000000006</v>
       </c>
       <c r="AN58" t="s">
         <v>238</v>
@@ -71372,7 +71372,7 @@
         <v>288</v>
       </c>
       <c r="AM69">
-        <v>0.41650000000000004</v>
+        <v>0.41649999999999993</v>
       </c>
       <c r="AN69" t="s">
         <v>238</v>
@@ -71472,7 +71472,7 @@
         <v>285</v>
       </c>
       <c r="AM71">
-        <v>0.33513333333333334</v>
+        <v>0.33513333333333328</v>
       </c>
       <c r="AN71" t="s">
         <v>238</v>
@@ -71672,7 +71672,7 @@
         <v>285</v>
       </c>
       <c r="AM75">
-        <v>0.34396666666666659</v>
+        <v>0.3439666666666667</v>
       </c>
       <c r="AN75" t="s">
         <v>238</v>
@@ -71922,7 +71922,7 @@
         <v>287</v>
       </c>
       <c r="AM80">
-        <v>0.43246666666666661</v>
+        <v>0.43246666666666672</v>
       </c>
       <c r="AN80" t="s">
         <v>238</v>
@@ -72072,7 +72072,7 @@
         <v>285</v>
       </c>
       <c r="AM83">
-        <v>0.33959999999999996</v>
+        <v>0.33960000000000007</v>
       </c>
       <c r="AN83" t="s">
         <v>238</v>
@@ -72172,7 +72172,7 @@
         <v>288</v>
       </c>
       <c r="AM85">
-        <v>0.42773333333333335</v>
+        <v>0.4277333333333333</v>
       </c>
       <c r="AN85" t="s">
         <v>238</v>
@@ -72272,7 +72272,7 @@
         <v>285</v>
       </c>
       <c r="AM87">
-        <v>0.33723333333333333</v>
+        <v>0.33723333333333327</v>
       </c>
       <c r="AN87" t="s">
         <v>238</v>
@@ -72622,7 +72622,7 @@
         <v>290</v>
       </c>
       <c r="AM94">
-        <v>0.36520000000000002</v>
+        <v>0.36519999999999997</v>
       </c>
       <c r="AN94" t="s">
         <v>238</v>
@@ -72772,7 +72772,7 @@
         <v>288</v>
       </c>
       <c r="AM97">
-        <v>0.44469999999999993</v>
+        <v>0.44470000000000004</v>
       </c>
       <c r="AN97" t="s">
         <v>238</v>
@@ -73022,7 +73022,7 @@
         <v>290</v>
       </c>
       <c r="AM102">
-        <v>0.3637333333333333</v>
+        <v>0.36373333333333341</v>
       </c>
       <c r="AN102" t="s">
         <v>238</v>
@@ -73222,7 +73222,7 @@
         <v>290</v>
       </c>
       <c r="AM106">
-        <v>0.3671666666666667</v>
+        <v>0.36716666666666664</v>
       </c>
       <c r="AN106" t="s">
         <v>238</v>
@@ -74072,7 +74072,7 @@
         <v>285</v>
       </c>
       <c r="AM123">
-        <v>0.33443333333333336</v>
+        <v>0.3344333333333333</v>
       </c>
       <c r="AN123" t="s">
         <v>238</v>

--- a/VerveStacks_DEU_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_DEU_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FF0B702-9390-4262-84A4-90CFFF379BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1EEF702-A5E7-42D9-A23B-FCD0D39EB15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -778,13 +778,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH02,S03aH01,S02aH02,S01aH02,S02aH01,S01aH01</t>
+    <t>S03aH01,S01aH01,S01aH02,S02aH02,S03aH02,S02aH01</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH03,S01aH03,S02aH03</t>
+    <t>S02aH03,S01aH03,S03aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -922,10 +922,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S02aH03,S07aH03,S02aH02,S05aH04,S06aH02,S06aH03,S01aH02,S04aH04,S03aH04,S04aH03,S07aH04,S03aH03,S04aH02,S02aH04,S02aH05,S01aH03,S05aH02,S05aH03,S03aH02,S07aH05,S01aH04,S07aH02,S04aH05,S03aH05,S05aH05,S06aH04,S01aH05,S06aH05</t>
+    <t>S02aH04,S02aH05,S03aH03,S04aH02,S01aH05,S06aH05,S03aH05,S05aH05,S06aH04,S03aH04,S04aH03,S07aH04,S01aH02,S04aH04,S01aH04,S07aH02,S01aH03,S05aH02,S05aH03,S05aH04,S06aH02,S06aH03,S04aH05,S03aH02,S07aH05,S02aH03,S07aH03,S02aH02</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S04aH06,S03aH01,S01aH06,S07aH01,S03aH06,S05aH01,S07aH06,S02aH01,S05aH06,S06aH06,S02aH06,S06aH01</t>
+    <t>S02aH06,S06aH06,S06aH01,S05aH01,S07aH06,S02aH01,S05aH06,S03aH06,S01aH06,S07aH01,S01aH01,S04aH01,S04aH06,S03aH01</t>
   </si>
   <si>
     <t>AllS</t>
@@ -991,10 +991,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,RaP,RaD,WaP,FaD,FaP,SaP,WaD</t>
+    <t>FaP,SaP,RaP,WaP,RaD,SaD,WaD,FaD</t>
   </si>
   <si>
-    <t>FaP,SaP,SaN,WaN,RaN,RaP,WaP,FaN</t>
+    <t>SaN,WaN,RaN,FaP,SaP,RaP,FaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24655,7 +24655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F82E93-A9E7-4485-882D-67D18E386582}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3A856A-AD04-45D9-BB4E-9B9BAA38B957}">
   <dimension ref="A9:AN217"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25222,7 +25222,7 @@
         <v>159</v>
       </c>
       <c r="AM15">
-        <v>0.43010548667828763</v>
+        <v>0.43010548667828769</v>
       </c>
       <c r="AN15" t="s">
         <v>238</v>
@@ -26014,7 +26014,7 @@
         <v>159</v>
       </c>
       <c r="AM27">
-        <v>0.34229999999999999</v>
+        <v>0.34230000000000005</v>
       </c>
       <c r="AN27" t="s">
         <v>238</v>
@@ -26173,7 +26173,7 @@
         <v>159</v>
       </c>
       <c r="AM30">
-        <v>0.34950000000000003</v>
+        <v>0.34949999999999998</v>
       </c>
       <c r="AN30" t="s">
         <v>238</v>
@@ -26923,7 +26923,7 @@
         <v>159</v>
       </c>
       <c r="AM45">
-        <v>0.41043749999999996</v>
+        <v>0.41043750000000001</v>
       </c>
       <c r="AN45" t="s">
         <v>238</v>
@@ -27073,7 +27073,7 @@
         <v>159</v>
       </c>
       <c r="AM48">
-        <v>0.41247500000000004</v>
+        <v>0.41247499999999998</v>
       </c>
       <c r="AN48" t="s">
         <v>238</v>
@@ -27373,7 +27373,7 @@
         <v>159</v>
       </c>
       <c r="AM54">
-        <v>0.40180000000000005</v>
+        <v>0.40179999999999993</v>
       </c>
       <c r="AN54" t="s">
         <v>238</v>
@@ -27523,7 +27523,7 @@
         <v>159</v>
       </c>
       <c r="AM57">
-        <v>0.39618750000000003</v>
+        <v>0.39618749999999997</v>
       </c>
       <c r="AN57" t="s">
         <v>238</v>
@@ -27823,7 +27823,7 @@
         <v>159</v>
       </c>
       <c r="AM63">
-        <v>0.40827499999999994</v>
+        <v>0.408275</v>
       </c>
       <c r="AN63" t="s">
         <v>238</v>
@@ -28723,7 +28723,7 @@
         <v>159</v>
       </c>
       <c r="AM81">
-        <v>0.39603749999999993</v>
+        <v>0.39603750000000004</v>
       </c>
       <c r="AN81" t="s">
         <v>238</v>
@@ -29023,7 +29023,7 @@
         <v>159</v>
       </c>
       <c r="AM87">
-        <v>0.40883750000000002</v>
+        <v>0.40883749999999996</v>
       </c>
       <c r="AN87" t="s">
         <v>238</v>
@@ -29323,7 +29323,7 @@
         <v>159</v>
       </c>
       <c r="AM93">
-        <v>0.4075125</v>
+        <v>0.40751250000000006</v>
       </c>
       <c r="AN93" t="s">
         <v>238</v>
@@ -32583,7 +32583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D305863-F5C1-47F8-B858-8F96A8079EC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE03E6D9-5DBB-469C-91BB-A8DBDE31609B}">
   <dimension ref="A9:AN976"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34300,7 +34300,7 @@
         <v>242</v>
       </c>
       <c r="AM29">
-        <v>0.34101200270411608</v>
+        <v>0.34101200270411602</v>
       </c>
       <c r="AN29" t="s">
         <v>238</v>
@@ -35420,7 +35420,7 @@
         <v>242</v>
       </c>
       <c r="AM43">
-        <v>0.32382000000000005</v>
+        <v>0.32382</v>
       </c>
       <c r="AN43" t="s">
         <v>238</v>
@@ -37261,7 +37261,7 @@
         <v>242</v>
       </c>
       <c r="AM71">
-        <v>0.35035999999999995</v>
+        <v>0.35036</v>
       </c>
       <c r="AN71" t="s">
         <v>238</v>
@@ -39918,7 +39918,7 @@
         <v>242</v>
       </c>
       <c r="AM120">
-        <v>0.37729999999999997</v>
+        <v>0.37730000000000008</v>
       </c>
       <c r="AN120" t="s">
         <v>238</v>
@@ -40268,7 +40268,7 @@
         <v>242</v>
       </c>
       <c r="AM127">
-        <v>0.39102000000000003</v>
+        <v>0.39101999999999998</v>
       </c>
       <c r="AN127" t="s">
         <v>238</v>
@@ -41318,7 +41318,7 @@
         <v>242</v>
       </c>
       <c r="AM148">
-        <v>0.38604000000000005</v>
+        <v>0.38603999999999999</v>
       </c>
       <c r="AN148" t="s">
         <v>238</v>
@@ -42368,7 +42368,7 @@
         <v>242</v>
       </c>
       <c r="AM169">
-        <v>0.40208000000000005</v>
+        <v>0.40207999999999994</v>
       </c>
       <c r="AN169" t="s">
         <v>238</v>
@@ -43068,7 +43068,7 @@
         <v>242</v>
       </c>
       <c r="AM183">
-        <v>0.40821999999999992</v>
+        <v>0.40822000000000003</v>
       </c>
       <c r="AN183" t="s">
         <v>238</v>
@@ -66518,7 +66518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3221F889-51DF-40CB-BFDD-248268D9FEA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C641A1A1-C865-4E58-B695-F1719E256928}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -67006,7 +67006,7 @@
         <v>282</v>
       </c>
       <c r="AM16">
-        <v>0.32494166666666668</v>
+        <v>0.32494166666666663</v>
       </c>
       <c r="AN16" t="s">
         <v>238</v>
@@ -67320,7 +67320,7 @@
         <v>282</v>
       </c>
       <c r="AM23">
-        <v>0.38800833333333334</v>
+        <v>0.38800833333333329</v>
       </c>
       <c r="AN23" t="s">
         <v>238</v>
@@ -67396,7 +67396,7 @@
         <v>282</v>
       </c>
       <c r="AM25">
-        <v>0.38934166666666664</v>
+        <v>0.3893416666666667</v>
       </c>
       <c r="AN25" t="s">
         <v>238</v>
@@ -67472,7 +67472,7 @@
         <v>282</v>
       </c>
       <c r="AM27">
-        <v>0.37600000000000006</v>
+        <v>0.37599999999999995</v>
       </c>
       <c r="AN27" t="s">
         <v>238</v>
@@ -67624,7 +67624,7 @@
         <v>282</v>
       </c>
       <c r="AM31">
-        <v>0.38801666666666668</v>
+        <v>0.38801666666666662</v>
       </c>
       <c r="AN31" t="s">
         <v>238</v>
@@ -67662,7 +67662,7 @@
         <v>282</v>
       </c>
       <c r="AM32">
-        <v>0.38476666666666665</v>
+        <v>0.3847666666666667</v>
       </c>
       <c r="AN32" t="s">
         <v>238</v>
@@ -67688,7 +67688,7 @@
         <v>282</v>
       </c>
       <c r="AM33">
-        <v>0.39074999999999999</v>
+        <v>0.3907500000000001</v>
       </c>
       <c r="AN33" t="s">
         <v>238</v>
@@ -67716,7 +67716,7 @@
         <v>282</v>
       </c>
       <c r="AM35">
-        <v>0.3848833333333333</v>
+        <v>0.38488333333333324</v>
       </c>
       <c r="AN35" t="s">
         <v>238</v>
@@ -67730,7 +67730,7 @@
         <v>282</v>
       </c>
       <c r="AM36">
-        <v>0.38367500000000004</v>
+        <v>0.38367499999999999</v>
       </c>
       <c r="AN36" t="s">
         <v>238</v>
@@ -67744,7 +67744,7 @@
         <v>282</v>
       </c>
       <c r="AM37">
-        <v>0.38875833333333326</v>
+        <v>0.38875833333333332</v>
       </c>
       <c r="AN37" t="s">
         <v>238</v>
@@ -67758,7 +67758,7 @@
         <v>282</v>
       </c>
       <c r="AM38">
-        <v>0.38937499999999997</v>
+        <v>0.38937500000000003</v>
       </c>
       <c r="AN38" t="s">
         <v>238</v>
@@ -67772,7 +67772,7 @@
         <v>282</v>
       </c>
       <c r="AM39">
-        <v>0.37451666666666666</v>
+        <v>0.37451666666666661</v>
       </c>
       <c r="AN39" t="s">
         <v>238</v>
@@ -67784,7 +67784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B0BEA4-9ACF-4856-B8CB-094C97024D70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4864DB03-80D7-4190-B5B4-52BF89FB87BD}">
   <dimension ref="A9:AN286"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -68102,7 +68102,7 @@
         <v>287</v>
       </c>
       <c r="AM12">
-        <v>0.39410081878267733</v>
+        <v>0.39410081878267728</v>
       </c>
       <c r="AN12" t="s">
         <v>238</v>
@@ -68354,7 +68354,7 @@
         <v>285</v>
       </c>
       <c r="AM15">
-        <v>0.32311381832505287</v>
+        <v>0.32311381832505282</v>
       </c>
       <c r="AN15" t="s">
         <v>238</v>
@@ -69091,7 +69091,7 @@
         <v>288</v>
       </c>
       <c r="AM25">
-        <v>0.44846666666666674</v>
+        <v>0.44846666666666662</v>
       </c>
       <c r="AN25" t="s">
         <v>238</v>
@@ -69209,7 +69209,7 @@
         <v>285</v>
       </c>
       <c r="AM27">
-        <v>0.28350000000000003</v>
+        <v>0.28349999999999997</v>
       </c>
       <c r="AN27" t="s">
         <v>238</v>
@@ -70072,7 +70072,7 @@
         <v>285</v>
       </c>
       <c r="AM43">
-        <v>0.29210000000000003</v>
+        <v>0.29209999999999997</v>
       </c>
       <c r="AN43" t="s">
         <v>238</v>
@@ -70272,7 +70272,7 @@
         <v>285</v>
       </c>
       <c r="AM47">
-        <v>0.28259999999999996</v>
+        <v>0.28260000000000002</v>
       </c>
       <c r="AN47" t="s">
         <v>238</v>
@@ -70922,7 +70922,7 @@
         <v>287</v>
       </c>
       <c r="AM60">
-        <v>0.40096666666666664</v>
+        <v>0.40096666666666669</v>
       </c>
       <c r="AN60" t="s">
         <v>238</v>
@@ -71372,7 +71372,7 @@
         <v>288</v>
       </c>
       <c r="AM69">
-        <v>0.41649999999999993</v>
+        <v>0.41650000000000004</v>
       </c>
       <c r="AN69" t="s">
         <v>238</v>
@@ -71472,7 +71472,7 @@
         <v>285</v>
       </c>
       <c r="AM71">
-        <v>0.33513333333333328</v>
+        <v>0.33513333333333334</v>
       </c>
       <c r="AN71" t="s">
         <v>238</v>
@@ -71872,7 +71872,7 @@
         <v>285</v>
       </c>
       <c r="AM79">
-        <v>0.34176666666666661</v>
+        <v>0.34176666666666672</v>
       </c>
       <c r="AN79" t="s">
         <v>238</v>
@@ -72172,7 +72172,7 @@
         <v>288</v>
       </c>
       <c r="AM85">
-        <v>0.4277333333333333</v>
+        <v>0.42773333333333335</v>
       </c>
       <c r="AN85" t="s">
         <v>238</v>
@@ -72272,7 +72272,7 @@
         <v>285</v>
       </c>
       <c r="AM87">
-        <v>0.33723333333333327</v>
+        <v>0.33723333333333333</v>
       </c>
       <c r="AN87" t="s">
         <v>238</v>
@@ -72672,7 +72672,7 @@
         <v>285</v>
       </c>
       <c r="AM95">
-        <v>0.33693333333333331</v>
+        <v>0.33693333333333336</v>
       </c>
       <c r="AN95" t="s">
         <v>238</v>
@@ -72722,7 +72722,7 @@
         <v>287</v>
       </c>
       <c r="AM96">
-        <v>0.40823333333333339</v>
+        <v>0.40823333333333328</v>
       </c>
       <c r="AN96" t="s">
         <v>238</v>
@@ -72772,7 +72772,7 @@
         <v>288</v>
       </c>
       <c r="AM97">
-        <v>0.44470000000000004</v>
+        <v>0.44469999999999993</v>
       </c>
       <c r="AN97" t="s">
         <v>238</v>
@@ -73072,7 +73072,7 @@
         <v>285</v>
       </c>
       <c r="AM103">
-        <v>0.33239999999999997</v>
+        <v>0.33240000000000003</v>
       </c>
       <c r="AN103" t="s">
         <v>238</v>
@@ -73322,7 +73322,7 @@
         <v>287</v>
       </c>
       <c r="AM108">
-        <v>0.39473333333333338</v>
+        <v>0.39473333333333332</v>
       </c>
       <c r="AN108" t="s">
         <v>238</v>

--- a/VerveStacks_DEU_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_DEU_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1EEF702-A5E7-42D9-A23B-FCD0D39EB15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAAAD7A0-A484-4373-A161-FFF26DBE5431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -778,13 +778,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH01,S01aH01,S01aH02,S02aH02,S03aH02,S02aH01</t>
+    <t>S03aH01,S01aH02,S02aH02,S02aH01,S01aH01,S03aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH03,S01aH03,S03aH03</t>
+    <t>S03aH03,S02aH03,S01aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -922,10 +922,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S03aH03,S04aH02,S01aH05,S06aH05,S03aH05,S05aH05,S06aH04,S03aH04,S04aH03,S07aH04,S01aH02,S04aH04,S01aH04,S07aH02,S01aH03,S05aH02,S05aH03,S05aH04,S06aH02,S06aH03,S04aH05,S03aH02,S07aH05,S02aH03,S07aH03,S02aH02</t>
+    <t>S02aH02,S01aH03,S05aH02,S05aH03,S03aH02,S07aH05,S03aH04,S04aH03,S07aH04,S02aH03,S07aH03,S04aH05,S01aH04,S07aH02,S03aH03,S05aH04,S06aH02,S06aH03,S01aH05,S06aH05,S02aH04,S02aH05,S04aH02,S01aH02,S04aH04,S03aH05,S05aH05,S06aH04</t>
   </si>
   <si>
-    <t>S02aH06,S06aH06,S06aH01,S05aH01,S07aH06,S02aH01,S05aH06,S03aH06,S01aH06,S07aH01,S01aH01,S04aH01,S04aH06,S03aH01</t>
+    <t>S03aH01,S05aH01,S07aH06,S02aH01,S05aH06,S01aH01,S04aH01,S04aH06,S06aH01,S06aH06,S01aH06,S07aH01,S02aH06,S03aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -991,10 +991,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,WaP,RaD,SaD,WaD,FaD</t>
+    <t>SaD,WaP,FaP,SaP,FaD,WaD,RaP,RaD</t>
   </si>
   <si>
-    <t>SaN,WaN,RaN,FaP,SaP,RaP,FaN,WaP</t>
+    <t>FaP,SaP,FaN,RaN,SaN,WaN,RaP,WaP</t>
   </si>
 </sst>
 </file>
@@ -24655,7 +24655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3A856A-AD04-45D9-BB4E-9B9BAA38B957}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D27D99E-1284-4FEB-ABED-DBD8FB57C574}">
   <dimension ref="A9:AN217"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25222,7 +25222,7 @@
         <v>159</v>
       </c>
       <c r="AM15">
-        <v>0.43010548667828769</v>
+        <v>0.43010548667828774</v>
       </c>
       <c r="AN15" t="s">
         <v>238</v>
@@ -26173,7 +26173,7 @@
         <v>159</v>
       </c>
       <c r="AM30">
-        <v>0.34949999999999998</v>
+        <v>0.34950000000000003</v>
       </c>
       <c r="AN30" t="s">
         <v>238</v>
@@ -26323,7 +26323,7 @@
         <v>159</v>
       </c>
       <c r="AM33">
-        <v>0.34661249999999999</v>
+        <v>0.34661250000000005</v>
       </c>
       <c r="AN33" t="s">
         <v>238</v>
@@ -26623,7 +26623,7 @@
         <v>159</v>
       </c>
       <c r="AM39">
-        <v>0.34997499999999998</v>
+        <v>0.34997500000000004</v>
       </c>
       <c r="AN39" t="s">
         <v>238</v>
@@ -27073,7 +27073,7 @@
         <v>159</v>
       </c>
       <c r="AM48">
-        <v>0.41247499999999998</v>
+        <v>0.41247499999999993</v>
       </c>
       <c r="AN48" t="s">
         <v>238</v>
@@ -27223,7 +27223,7 @@
         <v>159</v>
       </c>
       <c r="AM51">
-        <v>0.39564999999999995</v>
+        <v>0.39565000000000006</v>
       </c>
       <c r="AN51" t="s">
         <v>238</v>
@@ -28423,7 +28423,7 @@
         <v>159</v>
       </c>
       <c r="AM75">
-        <v>0.40817499999999995</v>
+        <v>0.40817500000000007</v>
       </c>
       <c r="AN75" t="s">
         <v>238</v>
@@ -28723,7 +28723,7 @@
         <v>159</v>
       </c>
       <c r="AM81">
-        <v>0.39603750000000004</v>
+        <v>0.39603749999999993</v>
       </c>
       <c r="AN81" t="s">
         <v>238</v>
@@ -28873,7 +28873,7 @@
         <v>159</v>
       </c>
       <c r="AM84">
-        <v>0.40316249999999998</v>
+        <v>0.40316250000000003</v>
       </c>
       <c r="AN84" t="s">
         <v>238</v>
@@ -29023,7 +29023,7 @@
         <v>159</v>
       </c>
       <c r="AM87">
-        <v>0.40883749999999996</v>
+        <v>0.40883750000000002</v>
       </c>
       <c r="AN87" t="s">
         <v>238</v>
@@ -29323,7 +29323,7 @@
         <v>159</v>
       </c>
       <c r="AM93">
-        <v>0.40751250000000006</v>
+        <v>0.4075125</v>
       </c>
       <c r="AN93" t="s">
         <v>238</v>
@@ -32583,7 +32583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE03E6D9-5DBB-469C-91BB-A8DBDE31609B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8686C189-A753-4350-904B-70CB3ACF673B}">
   <dimension ref="A9:AN976"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33740,7 +33740,7 @@
         <v>242</v>
       </c>
       <c r="AM22">
-        <v>0.44703305455993625</v>
+        <v>0.44703305455993636</v>
       </c>
       <c r="AN22" t="s">
         <v>238</v>
@@ -34300,7 +34300,7 @@
         <v>242</v>
       </c>
       <c r="AM29">
-        <v>0.34101200270411602</v>
+        <v>0.34101200270411608</v>
       </c>
       <c r="AN29" t="s">
         <v>238</v>
@@ -37261,7 +37261,7 @@
         <v>242</v>
       </c>
       <c r="AM71">
-        <v>0.35036</v>
+        <v>0.35035999999999995</v>
       </c>
       <c r="AN71" t="s">
         <v>238</v>
@@ -37674,7 +37674,7 @@
         <v>242</v>
       </c>
       <c r="AM78">
-        <v>0.34266000000000002</v>
+        <v>0.34265999999999996</v>
       </c>
       <c r="AN78" t="s">
         <v>238</v>
@@ -38087,7 +38087,7 @@
         <v>242</v>
       </c>
       <c r="AM85">
-        <v>0.40323999999999999</v>
+        <v>0.4032400000000001</v>
       </c>
       <c r="AN85" t="s">
         <v>238</v>
@@ -38500,7 +38500,7 @@
         <v>242</v>
       </c>
       <c r="AM92">
-        <v>0.41478000000000004</v>
+        <v>0.41477999999999993</v>
       </c>
       <c r="AN92" t="s">
         <v>238</v>
@@ -39218,7 +39218,7 @@
         <v>242</v>
       </c>
       <c r="AM106">
-        <v>0.40088000000000001</v>
+        <v>0.4008799999999999</v>
       </c>
       <c r="AN106" t="s">
         <v>238</v>
@@ -39568,7 +39568,7 @@
         <v>242</v>
       </c>
       <c r="AM113">
-        <v>0.39846000000000004</v>
+        <v>0.39845999999999993</v>
       </c>
       <c r="AN113" t="s">
         <v>238</v>
@@ -39918,7 +39918,7 @@
         <v>242</v>
       </c>
       <c r="AM120">
-        <v>0.37730000000000008</v>
+        <v>0.37729999999999997</v>
       </c>
       <c r="AN120" t="s">
         <v>238</v>
@@ -41668,7 +41668,7 @@
         <v>242</v>
       </c>
       <c r="AM155">
-        <v>0.39388000000000001</v>
+        <v>0.39387999999999995</v>
       </c>
       <c r="AN155" t="s">
         <v>238</v>
@@ -42368,7 +42368,7 @@
         <v>242</v>
       </c>
       <c r="AM169">
-        <v>0.40207999999999994</v>
+        <v>0.40208000000000005</v>
       </c>
       <c r="AN169" t="s">
         <v>238</v>
@@ -43768,7 +43768,7 @@
         <v>242</v>
       </c>
       <c r="AM197">
-        <v>0.40364000000000005</v>
+        <v>0.40363999999999994</v>
       </c>
       <c r="AN197" t="s">
         <v>238</v>
@@ -44118,7 +44118,7 @@
         <v>242</v>
       </c>
       <c r="AM204">
-        <v>0.39583999999999997</v>
+        <v>0.39584000000000003</v>
       </c>
       <c r="AN204" t="s">
         <v>238</v>
@@ -66518,7 +66518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C641A1A1-C865-4E58-B695-F1719E256928}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{307724CD-B3B5-47F7-BDDF-82CF27F29898}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -66747,7 +66747,7 @@
         <v>282</v>
       </c>
       <c r="AM11">
-        <v>0.38802670653427351</v>
+        <v>0.38802670653427357</v>
       </c>
       <c r="AN11" t="s">
         <v>238</v>
@@ -67056,7 +67056,7 @@
         <v>282</v>
       </c>
       <c r="AM17">
-        <v>0.32603333333333329</v>
+        <v>0.32603333333333334</v>
       </c>
       <c r="AN17" t="s">
         <v>238</v>
@@ -67206,7 +67206,7 @@
         <v>282</v>
       </c>
       <c r="AM20">
-        <v>0.33071666666666666</v>
+        <v>0.33071666666666671</v>
       </c>
       <c r="AN20" t="s">
         <v>238</v>
@@ -67282,7 +67282,7 @@
         <v>282</v>
       </c>
       <c r="AM22">
-        <v>0.39006666666666673</v>
+        <v>0.39006666666666662</v>
       </c>
       <c r="AN22" t="s">
         <v>238</v>
@@ -67320,7 +67320,7 @@
         <v>282</v>
       </c>
       <c r="AM23">
-        <v>0.38800833333333329</v>
+        <v>0.38800833333333334</v>
       </c>
       <c r="AN23" t="s">
         <v>238</v>
@@ -67396,7 +67396,7 @@
         <v>282</v>
       </c>
       <c r="AM25">
-        <v>0.3893416666666667</v>
+        <v>0.38934166666666664</v>
       </c>
       <c r="AN25" t="s">
         <v>238</v>
@@ -67624,7 +67624,7 @@
         <v>282</v>
       </c>
       <c r="AM31">
-        <v>0.38801666666666662</v>
+        <v>0.38801666666666668</v>
       </c>
       <c r="AN31" t="s">
         <v>238</v>
@@ -67688,7 +67688,7 @@
         <v>282</v>
       </c>
       <c r="AM33">
-        <v>0.3907500000000001</v>
+        <v>0.39074999999999999</v>
       </c>
       <c r="AN33" t="s">
         <v>238</v>
@@ -67716,7 +67716,7 @@
         <v>282</v>
       </c>
       <c r="AM35">
-        <v>0.38488333333333324</v>
+        <v>0.38488333333333341</v>
       </c>
       <c r="AN35" t="s">
         <v>238</v>
@@ -67784,7 +67784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4864DB03-80D7-4190-B5B4-52BF89FB87BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D82BFC4-3A7E-44BB-B3E7-A353E2B38D9A}">
   <dimension ref="A9:AN286"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -68013,7 +68013,7 @@
         <v>285</v>
       </c>
       <c r="AM11">
-        <v>0.37689213332894894</v>
+        <v>0.376892133328949</v>
       </c>
       <c r="AN11" t="s">
         <v>238</v>
@@ -68102,7 +68102,7 @@
         <v>287</v>
       </c>
       <c r="AM12">
-        <v>0.39410081878267728</v>
+        <v>0.39410081878267733</v>
       </c>
       <c r="AN12" t="s">
         <v>238</v>
@@ -69209,7 +69209,7 @@
         <v>285</v>
       </c>
       <c r="AM27">
-        <v>0.28349999999999997</v>
+        <v>0.28350000000000003</v>
       </c>
       <c r="AN27" t="s">
         <v>238</v>
@@ -69386,7 +69386,7 @@
         <v>290</v>
       </c>
       <c r="AM30">
-        <v>0.29203333333333331</v>
+        <v>0.29203333333333337</v>
       </c>
       <c r="AN30" t="s">
         <v>238</v>
@@ -69822,7 +69822,7 @@
         <v>290</v>
       </c>
       <c r="AM38">
-        <v>0.28050000000000003</v>
+        <v>0.28049999999999997</v>
       </c>
       <c r="AN38" t="s">
         <v>238</v>
@@ -70022,7 +70022,7 @@
         <v>290</v>
       </c>
       <c r="AM42">
-        <v>0.31263333333333337</v>
+        <v>0.31263333333333332</v>
       </c>
       <c r="AN42" t="s">
         <v>238</v>
@@ -70822,7 +70822,7 @@
         <v>290</v>
       </c>
       <c r="AM58">
-        <v>0.34770000000000006</v>
+        <v>0.34769999999999995</v>
       </c>
       <c r="AN58" t="s">
         <v>238</v>
@@ -70922,7 +70922,7 @@
         <v>287</v>
       </c>
       <c r="AM60">
-        <v>0.40096666666666669</v>
+        <v>0.40096666666666664</v>
       </c>
       <c r="AN60" t="s">
         <v>238</v>
@@ -71672,7 +71672,7 @@
         <v>285</v>
       </c>
       <c r="AM75">
-        <v>0.3439666666666667</v>
+        <v>0.34396666666666659</v>
       </c>
       <c r="AN75" t="s">
         <v>238</v>
@@ -71872,7 +71872,7 @@
         <v>285</v>
       </c>
       <c r="AM79">
-        <v>0.34176666666666672</v>
+        <v>0.34176666666666661</v>
       </c>
       <c r="AN79" t="s">
         <v>238</v>
@@ -72072,7 +72072,7 @@
         <v>285</v>
       </c>
       <c r="AM83">
-        <v>0.33960000000000007</v>
+        <v>0.33959999999999996</v>
       </c>
       <c r="AN83" t="s">
         <v>238</v>
@@ -72622,7 +72622,7 @@
         <v>290</v>
       </c>
       <c r="AM94">
-        <v>0.36519999999999997</v>
+        <v>0.36520000000000002</v>
       </c>
       <c r="AN94" t="s">
         <v>238</v>
@@ -72672,7 +72672,7 @@
         <v>285</v>
       </c>
       <c r="AM95">
-        <v>0.33693333333333336</v>
+        <v>0.33693333333333331</v>
       </c>
       <c r="AN95" t="s">
         <v>238</v>
@@ -72722,7 +72722,7 @@
         <v>287</v>
       </c>
       <c r="AM96">
-        <v>0.40823333333333328</v>
+        <v>0.40823333333333339</v>
       </c>
       <c r="AN96" t="s">
         <v>238</v>
@@ -73022,7 +73022,7 @@
         <v>290</v>
       </c>
       <c r="AM102">
-        <v>0.36373333333333341</v>
+        <v>0.3637333333333333</v>
       </c>
       <c r="AN102" t="s">
         <v>238</v>
@@ -73072,7 +73072,7 @@
         <v>285</v>
       </c>
       <c r="AM103">
-        <v>0.33240000000000003</v>
+        <v>0.33239999999999997</v>
       </c>
       <c r="AN103" t="s">
         <v>238</v>
@@ -73222,7 +73222,7 @@
         <v>290</v>
       </c>
       <c r="AM106">
-        <v>0.36716666666666664</v>
+        <v>0.3671666666666667</v>
       </c>
       <c r="AN106" t="s">
         <v>238</v>
@@ -73322,7 +73322,7 @@
         <v>287</v>
       </c>
       <c r="AM108">
-        <v>0.39473333333333332</v>
+        <v>0.39473333333333338</v>
       </c>
       <c r="AN108" t="s">
         <v>238</v>
@@ -74072,7 +74072,7 @@
         <v>285</v>
       </c>
       <c r="AM123">
-        <v>0.3344333333333333</v>
+        <v>0.33443333333333336</v>
       </c>
       <c r="AN123" t="s">
         <v>238</v>
